--- a/eval/qlora/statistical_tests_full150.xlsx
+++ b/eval/qlora/statistical_tests_full150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,11 +498,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0064</v>
+        <v>0.017</v>
       </c>
       <c r="F2" t="n">
         <v>0.853</v>
@@ -517,7 +517,7 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0341</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.017</v>
+        <v>0.0129</v>
       </c>
       <c r="F3" t="n">
         <v>0.853</v>
       </c>
       <c r="G3" t="n">
-        <v>0.875</v>
+        <v>0.83</v>
       </c>
       <c r="H3" t="n">
         <v>0.0919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="J3" t="n">
         <v>0.0547</v>
@@ -563,12 +563,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,32 +578,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.00511</v>
+        <v>0.114</v>
       </c>
       <c r="F4" t="n">
-        <v>0.853</v>
+        <v>0.787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.83</v>
+        <v>0.803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0919</v>
+        <v>0.115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.091</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0341</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,28 +622,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0129</v>
+        <v>0.32</v>
       </c>
       <c r="F5" t="n">
-        <v>0.853</v>
+        <v>0.787</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>0.802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0919</v>
+        <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.091</v>
+        <v>0.102</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0547</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,47 +653,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>0.0934</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.147</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.09950000000000001</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.235</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -702,22 +702,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.114</v>
+        <v>0.0171</v>
       </c>
       <c r="F7" t="n">
-        <v>0.787</v>
+        <v>0.915</v>
       </c>
       <c r="G7" t="n">
-        <v>0.803</v>
+        <v>0.873</v>
       </c>
       <c r="H7" t="n">
-        <v>0.115</v>
+        <v>0.0954</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.144</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="8">
@@ -728,36 +728,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.305</v>
+        <v>0.632</v>
       </c>
       <c r="F8" t="n">
-        <v>0.787</v>
+        <v>0.842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.802</v>
+        <v>0.828</v>
       </c>
       <c r="H8" t="n">
-        <v>0.115</v>
+        <v>0.172</v>
       </c>
       <c r="I8" t="n">
-        <v>0.102</v>
+        <v>0.134</v>
       </c>
       <c r="J8" t="n">
-        <v>0.349</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="9">
@@ -773,7 +773,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.32</v>
+        <v>0.0736</v>
       </c>
       <c r="F9" t="n">
-        <v>0.787</v>
+        <v>0.842</v>
       </c>
       <c r="G9" t="n">
-        <v>0.802</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.115</v>
+        <v>0.172</v>
       </c>
       <c r="I9" t="n">
-        <v>0.102</v>
+        <v>0.185</v>
       </c>
       <c r="J9" t="n">
-        <v>0.341</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="10">
@@ -813,31 +813,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.185</v>
+        <v>0.0146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.915</v>
+        <v>0.706</v>
       </c>
       <c r="G10" t="n">
-        <v>0.884</v>
+        <v>0.753</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0954</v>
+        <v>0.164</v>
       </c>
       <c r="I10" t="n">
-        <v>0.147</v>
+        <v>0.198</v>
       </c>
       <c r="J10" t="n">
-        <v>0.269</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="11">
@@ -848,12 +848,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -862,68 +862,68 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0934</v>
+        <v>0.0309</v>
       </c>
       <c r="F11" t="n">
-        <v>0.915</v>
+        <v>0.706</v>
       </c>
       <c r="G11" t="n">
-        <v>0.884</v>
+        <v>0.666</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0954</v>
+        <v>0.164</v>
       </c>
       <c r="I11" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
       <c r="J11" t="n">
-        <v>0.136</v>
+        <v>0.0706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.915</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="n">
-        <v>0.873</v>
+        <v>0.629</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0954</v>
+        <v>0.147</v>
       </c>
       <c r="I12" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.125</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.0827</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -942,28 +942,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0171</v>
+        <v>0.048</v>
       </c>
       <c r="F13" t="n">
-        <v>0.915</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>0.873</v>
+        <v>0.624</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0954</v>
+        <v>0.147</v>
       </c>
       <c r="I13" t="n">
-        <v>0.125</v>
+        <v>0.172</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0547</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -973,47 +973,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.548</v>
+        <v>0.0214</v>
       </c>
       <c r="F14" t="n">
-        <v>0.842</v>
+        <v>0.791</v>
       </c>
       <c r="G14" t="n">
-        <v>0.828</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.172</v>
+        <v>0.137</v>
       </c>
       <c r="I14" t="n">
-        <v>0.134</v>
+        <v>0.174</v>
       </c>
       <c r="J14" t="n">
-        <v>0.548</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1022,22 +1022,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.632</v>
+        <v>0.0155</v>
       </c>
       <c r="F15" t="n">
-        <v>0.842</v>
+        <v>0.791</v>
       </c>
       <c r="G15" t="n">
-        <v>0.828</v>
+        <v>0.75</v>
       </c>
       <c r="H15" t="n">
-        <v>0.172</v>
+        <v>0.137</v>
       </c>
       <c r="I15" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="J15" t="n">
-        <v>0.632</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="16">
@@ -1048,36 +1048,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>wilcoxon</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.129</v>
+        <v>0.117</v>
       </c>
       <c r="F16" t="n">
-        <v>0.842</v>
+        <v>0.681</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H16" t="n">
-        <v>0.172</v>
+        <v>0.149</v>
       </c>
       <c r="I16" t="n">
-        <v>0.185</v>
+        <v>0.111</v>
       </c>
       <c r="J16" t="n">
-        <v>0.229</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="17">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1102,661 +1102,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0736</v>
+        <v>0.233</v>
       </c>
       <c r="F17" t="n">
-        <v>0.842</v>
+        <v>0.681</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="H17" t="n">
-        <v>0.172</v>
+        <v>0.149</v>
       </c>
       <c r="I17" t="n">
-        <v>0.185</v>
+        <v>0.168</v>
       </c>
       <c r="J17" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.00519</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.0341</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.0547</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.0592</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0706</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0673</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.07829999999999999</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0503</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>recall</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.096</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.337</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.0571</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.0424</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.0547</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.144</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>t-test</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.442</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="J33" t="n">
         <v>0.266</v>
       </c>
     </row>

--- a/eval/qlora/statistical_tests_full150.xlsx
+++ b/eval/qlora/statistical_tests_full150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -502,22 +502,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.017</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0.853</v>
       </c>
       <c r="G2" t="n">
-        <v>0.875</v>
+        <v>0.84</v>
       </c>
       <c r="H2" t="n">
         <v>0.0919</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,33 +542,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0129</v>
+        <v>0.017</v>
       </c>
       <c r="F3" t="n">
         <v>0.853</v>
       </c>
       <c r="G3" t="n">
-        <v>0.83</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
         <v>0.0919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.091</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0547</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.114</v>
+        <v>0.0129</v>
       </c>
       <c r="F4" t="n">
-        <v>0.787</v>
+        <v>0.853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.803</v>
+        <v>0.83</v>
       </c>
       <c r="H4" t="n">
-        <v>0.115</v>
+        <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="J4" t="n">
-        <v>0.144</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.32</v>
+        <v>0.442</v>
       </c>
       <c r="F5" t="n">
         <v>0.787</v>
       </c>
       <c r="G5" t="n">
-        <v>0.802</v>
+        <v>0.797</v>
       </c>
       <c r="H5" t="n">
         <v>0.115</v>
@@ -637,13 +637,13 @@
         <v>0.102</v>
       </c>
       <c r="J5" t="n">
-        <v>0.341</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -662,28 +662,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0934</v>
+        <v>0.114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.915</v>
+        <v>0.787</v>
       </c>
       <c r="G6" t="n">
-        <v>0.884</v>
+        <v>0.803</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0954</v>
+        <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>0.147</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.136</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -702,33 +702,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0171</v>
+        <v>0.32</v>
       </c>
       <c r="F7" t="n">
-        <v>0.915</v>
+        <v>0.787</v>
       </c>
       <c r="G7" t="n">
-        <v>0.873</v>
+        <v>0.802</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0954</v>
+        <v>0.115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.125</v>
+        <v>0.102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0547</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.632</v>
+        <v>0.00058</v>
       </c>
       <c r="F8" t="n">
-        <v>0.842</v>
+        <v>0.915</v>
       </c>
       <c r="G8" t="n">
-        <v>0.828</v>
+        <v>0.803</v>
       </c>
       <c r="H8" t="n">
-        <v>0.172</v>
+        <v>0.0954</v>
       </c>
       <c r="I8" t="n">
-        <v>0.134</v>
+        <v>0.197</v>
       </c>
       <c r="J8" t="n">
-        <v>0.632</v>
+        <v>0.00696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0736</v>
+        <v>0.0934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.842</v>
+        <v>0.915</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.884</v>
       </c>
       <c r="H9" t="n">
-        <v>0.172</v>
+        <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.185</v>
+        <v>0.147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.125</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="10">
@@ -808,12 +808,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -822,38 +822,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0146</v>
+        <v>0.0171</v>
       </c>
       <c r="F10" t="n">
-        <v>0.706</v>
+        <v>0.915</v>
       </c>
       <c r="G10" t="n">
-        <v>0.753</v>
+        <v>0.873</v>
       </c>
       <c r="H10" t="n">
-        <v>0.164</v>
+        <v>0.0954</v>
       </c>
       <c r="I10" t="n">
-        <v>0.198</v>
+        <v>0.125</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0547</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -862,22 +862,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0309</v>
+        <v>0.0248</v>
       </c>
       <c r="F11" t="n">
-        <v>0.706</v>
+        <v>0.842</v>
       </c>
       <c r="G11" t="n">
-        <v>0.666</v>
+        <v>0.804</v>
       </c>
       <c r="H11" t="n">
-        <v>0.164</v>
+        <v>0.172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.152</v>
+        <v>0.178</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0706</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="12">
@@ -893,7 +893,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58</v>
+        <v>0.842</v>
       </c>
       <c r="G12" t="n">
-        <v>0.629</v>
+        <v>0.828</v>
       </c>
       <c r="H12" t="n">
-        <v>0.147</v>
+        <v>0.172</v>
       </c>
       <c r="I12" t="n">
-        <v>0.117</v>
+        <v>0.134</v>
       </c>
       <c r="J12" t="n">
-        <v>0.125</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="13">
@@ -933,7 +933,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.048</v>
+        <v>0.0736</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>0.842</v>
       </c>
       <c r="G13" t="n">
-        <v>0.624</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.147</v>
+        <v>0.172</v>
       </c>
       <c r="I13" t="n">
-        <v>0.172</v>
+        <v>0.185</v>
       </c>
       <c r="J13" t="n">
-        <v>0.096</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="14">
@@ -968,12 +968,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0214</v>
+        <v>3.05e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.791</v>
+        <v>0.706</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.137</v>
+        <v>0.164</v>
       </c>
       <c r="I14" t="n">
-        <v>0.174</v>
+        <v>0.145</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0571</v>
+        <v>0.000732</v>
       </c>
     </row>
     <row r="15">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1022,38 +1022,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0155</v>
+        <v>0.0146</v>
       </c>
       <c r="F15" t="n">
-        <v>0.791</v>
+        <v>0.706</v>
       </c>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="H15" t="n">
-        <v>0.137</v>
+        <v>0.164</v>
       </c>
       <c r="I15" t="n">
-        <v>0.136</v>
+        <v>0.198</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0547</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.117</v>
+        <v>0.0309</v>
       </c>
       <c r="F16" t="n">
-        <v>0.681</v>
+        <v>0.706</v>
       </c>
       <c r="G16" t="n">
-        <v>0.71</v>
+        <v>0.666</v>
       </c>
       <c r="H16" t="n">
-        <v>0.149</v>
+        <v>0.164</v>
       </c>
       <c r="I16" t="n">
-        <v>0.111</v>
+        <v>0.152</v>
       </c>
       <c r="J16" t="n">
-        <v>0.144</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="17">
@@ -1088,36 +1088,356 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0629</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>wilcoxon</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0629</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0586</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.346</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>wilcoxon</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>0.233</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F25" t="n">
         <v>0.681</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G25" t="n">
         <v>0.698</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H25" t="n">
         <v>0.149</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I25" t="n">
         <v>0.168</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.266</v>
+      <c r="J25" t="n">
+        <v>0.311</v>
       </c>
     </row>
   </sheetData>

--- a/eval/qlora/statistical_tests_full150.xlsx
+++ b/eval/qlora/statistical_tests_full150.xlsx
@@ -508,7 +508,7 @@
         <v>0.853</v>
       </c>
       <c r="G2" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="H2" t="n">
         <v>0.0919</v>
@@ -557,7 +557,7 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0586</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         <v>0.091</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0586</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.442</v>
+        <v>0.425</v>
       </c>
       <c r="F5" t="n">
         <v>0.787</v>
@@ -634,10 +634,10 @@
         <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.102</v>
+        <v>0.101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.505</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="6">
@@ -837,7 +837,7 @@
         <v>0.125</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0586</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="11">
@@ -868,7 +868,7 @@
         <v>0.842</v>
       </c>
       <c r="G11" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="H11" t="n">
         <v>0.172</v>
@@ -877,7 +877,7 @@
         <v>0.178</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0629</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="12">
@@ -988,13 +988,13 @@
         <v>0.706</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>0.164</v>
       </c>
       <c r="I14" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="J14" t="n">
         <v>0.000732</v>
@@ -1037,7 +1037,7 @@
         <v>0.198</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0586</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="16">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0262</v>
+        <v>0.0214</v>
       </c>
       <c r="F17" t="n">
         <v>0.58</v>
       </c>
       <c r="G17" t="n">
-        <v>0.638</v>
+        <v>0.639</v>
       </c>
       <c r="H17" t="n">
         <v>0.147</v>
@@ -1117,7 +1117,7 @@
         <v>0.153</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0629</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="18">
@@ -1277,7 +1277,7 @@
         <v>0.174</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0629</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="22">
@@ -1317,7 +1317,7 @@
         <v>0.136</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0586</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="23">
@@ -1348,7 +1348,7 @@
         <v>0.681</v>
       </c>
       <c r="G23" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
       <c r="H23" t="n">
         <v>0.149</v>
